--- a/Data_Table/미니게임 테이블.xlsx
+++ b/Data_Table/미니게임 테이블.xlsx
@@ -877,15 +877,15 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>ten_pull</t>
+          <t>bulk_max</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>Shift + 뽑기 = 한 번에 뽑는 수</t>
+          <t>일괄 뽑기 (왼쪽 Ctrl · Ctrl + 뽑기 버튼) = 치즈가 되는 만큼 한 번에, 최대 이 마릿수</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>뽑기 버튼 꾹 누르기: 연속 시작까지 (초)</t>
+          <t>뽑기 버튼 · 왼쪽 Shift 꾹 누르기: 연속 시작까지 (초)</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,6 @@
           <t>쥐돌깨기 (뒷골목 미니 게임기) 설정 값. 판 = 1280×720 픽셀 (웹 프로토타입 쥐돌깨기.html 그대로)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2597,7 +2596,6 @@
           <t>쥐 등급별 피해 · 고유 스킬 확률 · 오라 · 색 (등급 이름 = 쥐 등급 테이블)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2610,7 +2608,6 @@
           <t>증강 16종: 이름·아이콘 = 증강 테이블 augment_id, 효과 = 이 게임 규칙. 값 = min(cap, v1 × 단계)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2623,7 +2620,6 @@
           <t>증강 고르기 3장의 등급 가중치 (등급 이름·색 = 증강 테이블 Grade)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2636,7 +2632,6 @@
           <t>벽돌 처음 체력 구간별 덧칠 색</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2649,7 +2644,6 @@
           <t>유니크↑ 고유 스킬 범위 모양: sq 3×3 · row 가로줄 · col 세로줄 · x 대각선 · (없으면 cross 십자). 신화는 3×3 도 같이</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data_Table/미니게임 테이블.xlsx
+++ b/Data_Table/미니게임 테이블.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>1.075</v>
+        <v>1.0775</v>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>증강 뽑기 재료 쥐 수 = aug_base × aug_mul^(뽑은 증강 수) — 낮은 등급·오래된 쥐부터</t>
+          <t>증강 뽑기 재료 쥐 수 = aug_base × aug_mul^(뽑은 증강 수) — aug_late_from 번째부터는 aug_mul_late 로 늘어남, 낮은 등급·오래된 쥐부터</t>
         </is>
       </c>
     </row>
@@ -1008,43 +1008,69 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>blade_radius</t>
+          <t>aug_late_from</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>회전 치즈 칼날 반지름 (판 픽셀)</t>
+          <t>이 번째 증강부터 비용 증가 배수 = aug_mul_late (그 전까지는 aug_mul) — 후반 비용이 확 뛰지 않게</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>blade_spin</t>
+          <t>aug_mul_late</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>칼날 회전 속도 (라디안/초)</t>
-        </is>
-      </c>
+        <v>1.3</v>
+      </c>
+      <c r="C41" s="1" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
+          <t>blade_radius</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>회전 치즈 칼날 반지름 (판 픽셀)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>blade_spin</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>칼날 회전 속도 (라디안/초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
           <t>blade_cd</t>
         </is>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B44" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>칼날이 같은 벽돌을 다시 칠 때까지 (초)</t>
         </is>
@@ -1475,7 +1501,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0</v>
@@ -1505,10 +1531,10 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2</v>
@@ -1595,10 +1621,10 @@
         <v>2</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>0</v>
@@ -1625,10 +1651,10 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>1</v>
@@ -1715,7 +1741,7 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>0</v>
@@ -1745,7 +1771,7 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>0</v>
@@ -1775,7 +1801,7 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>0</v>
@@ -1805,7 +1831,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0</v>
@@ -1835,7 +1861,7 @@
         <v>4</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>0</v>
@@ -1865,7 +1891,7 @@
         <v>4</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>0</v>
@@ -1895,7 +1921,7 @@
         <v>4</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>0</v>
@@ -1925,7 +1951,7 @@
         <v>4</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>0</v>
